--- a/Processed_Data.xlsx
+++ b/Processed_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FILES\Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FILES\Projects\TDF_Visual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4CC57F3-E91D-41AF-882B-8DFB32628F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAB75F3-02A8-401A-A261-B056C545EF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E470CF71-16E0-4BF9-BFEB-AEE72BA86962}"/>
   </bookViews>
@@ -199,10 +199,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -211,24 +226,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,200 +562,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="1" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="1" t="s">
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="3"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="N2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="P2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="6"/>
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2">
+        <v>78</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="2">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R4" s="6"/>
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="2">
+        <v>89</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="R5" s="9"/>
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="4">
+        <v>34</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4">
+        <v>67</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="5">
+        <v>90</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="4">
+        <v>33</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R5" s="5">
+        <v>99</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
